--- a/samples/示例登分表_八年级.xlsx
+++ b/samples/示例登分表_八年级.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>李浩怡</t>
+          <t>李书言</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>马浩杰</t>
+          <t>马书辰</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>罗雨宇</t>
+          <t>罗南白</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>张思涵</t>
+          <t>张星秋</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>罗浩远</t>
+          <t>罗书野</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>何浩远</t>
+          <t>何书野</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>朱欣桐</t>
+          <t>朱墨乔</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>马一怡</t>
+          <t>马疏言</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>何思诺</t>
+          <t>何星桐</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>林浩琪</t>
+          <t>林书澜</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>林欣怡</t>
+          <t>林墨言</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>刘明杰</t>
+          <t>刘和辰</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>刘浩轩</t>
+          <t>刘书禾</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>罗思轩</t>
+          <t>罗星舟</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>马梓琪</t>
+          <t>马青澜</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>孙佳宇</t>
+          <t>孙听白</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>孙明轩</t>
+          <t>孙和舟</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>周雨宇</t>
+          <t>周南白</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>黄思杰</t>
+          <t>黄星辰</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>杨明桐</t>
+          <t>杨和乔</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>张欣轩</t>
+          <t>张墨舟</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>张梓涵</t>
+          <t>张青秋</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>周雨怡</t>
+          <t>周南言</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>李子远</t>
+          <t>李砚野</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>陈欣轩</t>
+          <t>陈墨禾</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>朱雨轩</t>
+          <t>朱南舟</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>郭欣琪</t>
+          <t>郭墨澜</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>郭俊宇</t>
+          <t>郭北白</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杨俊轩</t>
+          <t>杨北舟</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>罗一诺</t>
+          <t>罗疏桐</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>李欣诺</t>
+          <t>李墨桐</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>王俊琪</t>
+          <t>王北澜</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>林浩诺</t>
+          <t>林书桐</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>何子宇</t>
+          <t>何砚白</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>赵一诺</t>
+          <t>赵疏桐</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>徐浩桐</t>
+          <t>徐书乔</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>刘雨远</t>
+          <t>刘南野</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>周雨轩</t>
+          <t>周南禾</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>王雨轩</t>
+          <t>王南禾</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>陈一轩</t>
+          <t>陈疏禾</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>罗欣杰</t>
+          <t>罗墨辰</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>赵一怡</t>
+          <t>赵疏言</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>吴浩宇</t>
+          <t>吴书白</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>赵子涵</t>
+          <t>赵砚秋</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>高子轩</t>
+          <t>高砚禾</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>周子杰</t>
+          <t>周砚辰</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>何俊怡</t>
+          <t>何北言</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>马明宇</t>
+          <t>马和白</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>黄思杰</t>
+          <t>黄星辰</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>刘思宇</t>
+          <t>刘星白</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>郭明涵</t>
+          <t>郭和秋</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>刘欣涵</t>
+          <t>刘墨秋</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>陈浩怡</t>
+          <t>陈书言</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>徐一宇</t>
+          <t>徐疏白</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>黄浩怡</t>
+          <t>黄书言</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>郭雨诺</t>
+          <t>郭南桐</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>王佳诺</t>
+          <t>王听桐</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>刘一怡</t>
+          <t>刘疏言</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>赵思轩</t>
+          <t>赵星禾</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>李一诺</t>
+          <t>李疏桐</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>周子远</t>
+          <t>周砚野</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>李思轩</t>
+          <t>李星舟</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>罗梓远</t>
+          <t>罗青野</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>吴一远</t>
+          <t>吴疏野</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>王欣远</t>
+          <t>王墨野</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>胡佳桐</t>
+          <t>胡听乔</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>郭思桐</t>
+          <t>郭星乔</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>朱一轩</t>
+          <t>朱疏禾</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>林欣诺</t>
+          <t>林墨桐</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>黄明宇</t>
+          <t>黄和白</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>刘明怡</t>
+          <t>刘和言</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>林子怡</t>
+          <t>林砚言</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>高雨怡</t>
+          <t>高南言</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>徐佳桐</t>
+          <t>徐听乔</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>陈欣杰</t>
+          <t>陈墨辰</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>周一远</t>
+          <t>周疏野</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>朱浩怡</t>
+          <t>朱书言</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>张雨诺</t>
+          <t>张南桐</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>李子宇</t>
+          <t>李砚白</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>罗俊诺</t>
+          <t>罗北桐</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>赵明怡</t>
+          <t>赵和言</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>黄雨琪</t>
+          <t>黄南澜</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>刘雨琪</t>
+          <t>刘南澜</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>李思涵</t>
+          <t>李星秋</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>徐明琪</t>
+          <t>徐和澜</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>陈明轩</t>
+          <t>陈和舟</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>朱思怡</t>
+          <t>朱星言</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>李雨怡</t>
+          <t>李南言</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>黄一杰</t>
+          <t>黄疏辰</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>徐欣怡</t>
+          <t>徐墨言</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>李欣杰</t>
+          <t>李墨辰</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>高一宇</t>
+          <t>高疏白</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>高雨涵</t>
+          <t>高南秋</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>朱浩轩</t>
+          <t>朱书禾</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>郭欣琪</t>
+          <t>郭墨澜</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>朱明诺</t>
+          <t>朱和桐</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>胡雨轩</t>
+          <t>胡南禾</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>孙浩远</t>
+          <t>孙书野</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>吴一轩</t>
+          <t>吴疏禾</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>朱浩轩</t>
+          <t>朱书禾</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>周思桐</t>
+          <t>周星乔</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>杨子琪</t>
+          <t>杨砚澜</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>马子琪</t>
+          <t>马砚澜</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>吴俊远</t>
+          <t>吴北野</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>王欣琪</t>
+          <t>王墨澜</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>刘梓轩</t>
+          <t>刘青禾</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>刘明轩</t>
+          <t>刘和禾</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>李一杰</t>
+          <t>李疏辰</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>张梓轩</t>
+          <t>张青舟</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>杨梓轩</t>
+          <t>杨青禾</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>朱子轩</t>
+          <t>朱砚舟</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>刘浩远</t>
+          <t>刘书野</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>张梓怡</t>
+          <t>张青言</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>李明琪</t>
+          <t>李和澜</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>张子轩</t>
+          <t>张砚禾</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>陈雨桐</t>
+          <t>陈南乔</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>朱浩琪</t>
+          <t>朱书澜</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>吴梓远</t>
+          <t>吴青野</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>王梓轩</t>
+          <t>王青舟</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>赵佳怡</t>
+          <t>赵听言</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>刘明轩</t>
+          <t>刘和舟</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>林欣涵</t>
+          <t>林墨秋</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>朱子诺</t>
+          <t>朱砚桐</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>张俊诺</t>
+          <t>张北桐</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>杨子桐</t>
+          <t>杨砚乔</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>胡明杰</t>
+          <t>胡和辰</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>罗思轩</t>
+          <t>罗星舟</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>高思琪</t>
+          <t>高星澜</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>高明诺</t>
+          <t>高和桐</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>杨浩杰</t>
+          <t>杨书辰</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>郭佳宇</t>
+          <t>郭听白</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>吴雨宇</t>
+          <t>吴南白</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>周佳远</t>
+          <t>周听野</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>高欣怡</t>
+          <t>高墨言</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>胡浩琪</t>
+          <t>胡书澜</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>赵欣远</t>
+          <t>赵墨野</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>陈子诺</t>
+          <t>陈砚桐</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>何俊桐</t>
+          <t>何北乔</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>林俊宇</t>
+          <t>林北白</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>何佳宇</t>
+          <t>何听白</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>何佳远</t>
+          <t>何听野</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>高明宇</t>
+          <t>高和白</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>高佳涵</t>
+          <t>高听秋</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>张浩琪</t>
+          <t>张书澜</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>吴佳涵</t>
+          <t>吴听秋</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>胡浩远</t>
+          <t>胡书野</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>刘俊琪</t>
+          <t>刘北澜</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>罗俊远</t>
+          <t>罗北野</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>张欣琪</t>
+          <t>张墨澜</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>朱明杰</t>
+          <t>朱和辰</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>郭思杰</t>
+          <t>郭星辰</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>李一杰</t>
+          <t>李疏辰</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>罗欣杰</t>
+          <t>罗墨辰</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>李雨杰</t>
+          <t>李南辰</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>罗明远</t>
+          <t>罗和野</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>张浩桐</t>
+          <t>张书乔</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>李一诺</t>
+          <t>李疏桐</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>孙梓杰</t>
+          <t>孙青辰</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>张俊宇</t>
+          <t>张北白</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>林浩宇</t>
+          <t>林书白</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>何思远</t>
+          <t>何星野</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>高梓诺</t>
+          <t>高青桐</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>郭俊远</t>
+          <t>郭北野</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>高佳轩</t>
+          <t>高听禾</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>罗梓杰</t>
+          <t>罗青辰</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>王欣怡</t>
+          <t>王墨言</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>刘欣轩</t>
+          <t>刘墨禾</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>黄一涵</t>
+          <t>黄疏秋</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>李欣轩</t>
+          <t>李墨禾</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>孙俊轩</t>
+          <t>孙北禾</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>吴欣远</t>
+          <t>吴墨野</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>王思杰</t>
+          <t>王星辰</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>孙欣琪</t>
+          <t>孙墨澜</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>郭雨诺</t>
+          <t>郭南桐</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>何一杰</t>
+          <t>何疏辰</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>黄一轩</t>
+          <t>黄疏舟</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>马雨宇</t>
+          <t>马南白</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>李梓诺</t>
+          <t>李青桐</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>刘雨宇</t>
+          <t>刘南白</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>马佳琪</t>
+          <t>马听澜</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>张子宇</t>
+          <t>张砚白</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>马思桐</t>
+          <t>马星乔</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>胡明轩</t>
+          <t>胡和舟</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>黄梓怡</t>
+          <t>黄青言</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>张梓宇</t>
+          <t>张青白</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>林一宇</t>
+          <t>林疏白</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>黄子诺</t>
+          <t>黄砚桐</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>郭梓诺</t>
+          <t>郭青桐</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>孙思轩</t>
+          <t>孙星舟</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>张浩诺</t>
+          <t>张书桐</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>赵一怡</t>
+          <t>赵疏言</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>罗雨桐</t>
+          <t>罗南乔</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>吴雨杰</t>
+          <t>吴南辰</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>徐俊轩</t>
+          <t>徐北舟</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>赵佳琪</t>
+          <t>赵听澜</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>林思轩</t>
+          <t>林星禾</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>王浩杰</t>
+          <t>王书辰</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>王思轩</t>
+          <t>王星舟</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>赵子怡</t>
+          <t>赵砚言</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>刘明桐</t>
+          <t>刘和乔</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>吴俊诺</t>
+          <t>吴北桐</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>马俊宇</t>
+          <t>马北白</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>杨子轩</t>
+          <t>杨砚禾</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>徐思轩</t>
+          <t>徐星禾</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>高俊琪</t>
+          <t>高北澜</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>李雨轩</t>
+          <t>李南舟</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>刘欣轩</t>
+          <t>刘墨禾</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>杨欣琪</t>
+          <t>杨墨澜</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>何佳诺</t>
+          <t>何听桐</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>林佳远</t>
+          <t>林听野</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>王明琪</t>
+          <t>王和澜</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>马明宇</t>
+          <t>马和白</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>周俊桐</t>
+          <t>周北乔</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>朱欣杰</t>
+          <t>朱墨辰</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>罗子诺</t>
+          <t>罗砚桐</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>罗雨桐</t>
+          <t>罗南乔</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>吴梓桐</t>
+          <t>吴青乔</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>马思涵</t>
+          <t>马星秋</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>马子桐</t>
+          <t>马砚乔</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>郭思琪</t>
+          <t>郭星澜</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>张欣杰</t>
+          <t>张墨辰</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>李明涵</t>
+          <t>李和秋</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>杨欣轩</t>
+          <t>杨墨禾</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>王浩怡</t>
+          <t>王书言</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>林一琪</t>
+          <t>林疏澜</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>胡明宇</t>
+          <t>胡和白</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>陈浩轩</t>
+          <t>陈书禾</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>赵一琪</t>
+          <t>赵疏澜</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>吴佳诺</t>
+          <t>吴听桐</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>王子诺</t>
+          <t>王砚桐</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>何梓杰</t>
+          <t>何青辰</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>王明怡</t>
+          <t>王和言</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>胡俊诺</t>
+          <t>胡北桐</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>李欣远</t>
+          <t>李墨野</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>刘欣远</t>
+          <t>刘墨野</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>徐佳远</t>
+          <t>徐听野</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>孙明远</t>
+          <t>孙和野</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>杨佳诺</t>
+          <t>杨听桐</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>张浩杰</t>
+          <t>张书辰</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>朱子远</t>
+          <t>朱砚野</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>陈一怡</t>
+          <t>陈疏言</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>朱欣轩</t>
+          <t>朱墨禾</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>赵明宇</t>
+          <t>赵和白</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>何思桐</t>
+          <t>何星乔</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>高俊杰</t>
+          <t>高北辰</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>周雨桐</t>
+          <t>周南乔</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>黄梓琪</t>
+          <t>黄青澜</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>孙欣诺</t>
+          <t>孙墨桐</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>罗欣轩</t>
+          <t>罗墨舟</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>吴欣远</t>
+          <t>吴墨野</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>李雨轩</t>
+          <t>李南舟</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>王梓杰</t>
+          <t>王青辰</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>王一远</t>
+          <t>王疏野</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>杨子怡</t>
+          <t>杨砚言</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>陈梓轩</t>
+          <t>陈青舟</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>陈欣宇</t>
+          <t>陈墨白</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>周一杰</t>
+          <t>周疏辰</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>徐俊桐</t>
+          <t>徐北乔</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>赵一怡</t>
+          <t>赵疏言</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>李俊轩</t>
+          <t>李北禾</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>刘佳涵</t>
+          <t>刘听秋</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>何俊远</t>
+          <t>何北野</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>马浩涵</t>
+          <t>马书秋</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>刘俊涵</t>
+          <t>刘北秋</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>杨一轩</t>
+          <t>杨疏舟</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>赵浩杰</t>
+          <t>赵书辰</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>朱浩轩</t>
+          <t>朱书禾</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>刘浩宇</t>
+          <t>刘书白</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>孙欣琪</t>
+          <t>孙墨澜</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>林一轩</t>
+          <t>林疏舟</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
